--- a/astro-site/public/dl/restaurant-financial-plan-templates/07-restaurant-loan-proposal-lender-summary.xlsx
+++ b/astro-site/public/dl/restaurant-financial-plan-templates/07-restaurant-loan-proposal-lender-summary.xlsx
@@ -199,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -330,6 +330,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="7" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -941,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B25"/>
+  <dimension ref="A2:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1021,14 +1024,14 @@
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>▸ Loan Schedule: loan amortization schedule. It feeds the interest in the P&amp;L, the loan payment in the DSCR and the loan payment line of the cash flow in file 03 "Cash Flow Forecast".</t>
+          <t>▸ Loan Schedule: loan amortization schedule. It feeds the interest in the P&amp;L and the payment in the DSCR. Copy the payment into file 03 "Cash Flow Forecast" yourself ("Monthly Cash Flow" tab, row 23, divided by 12).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>▸ Ratios: solvency and profitability indicators. DSCR compares the project's year 1 free cash flow ("Projections", row 17) with that year's debt service ("Loan Schedule"): it measures whether the business covers the payment.</t>
+          <t>▸ Ratios: solvency and profitability indicators. The DSCR at full payment compares the project's year 1 free cash flow ("Projections", row 17) with the full annual loan payment ("Loan Schedule", "ANNUAL PAYMENT"), even during an interest-only period: it measures whether the business covers the payment.</t>
         </is>
       </c>
     </row>
@@ -1074,6 +1077,13 @@
       <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Version 2.0 · October 2026 · aichef.pro/en/digital-products/restaurant-financial-plan-templates · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="B26" s="57" t="inlineStr">
+        <is>
+          <t>Planning tool, not financial, tax or legal advice. Requirements vary by state and city — check with your accountant and local authorities.</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1191,7 @@
           <t>Planned opening date</t>
         </is>
       </c>
-      <c r="C10" s="57" t="n"/>
+      <c r="C10" s="58" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
@@ -1196,7 +1206,7 @@
           <t>Total investment required</t>
         </is>
       </c>
-      <c r="C13" s="58" t="n"/>
+      <c r="C13" s="59" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="7" t="inlineStr">
@@ -1204,7 +1214,7 @@
           <t>Owner's equity contributed</t>
         </is>
       </c>
-      <c r="C14" s="58" t="n"/>
+      <c r="C14" s="59" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="7" t="inlineStr">
@@ -1212,7 +1222,7 @@
           <t>Financing requested</t>
         </is>
       </c>
-      <c r="C15" s="59">
+      <c r="C15" s="60">
         <f>'Loan Schedule'!$C$4</f>
         <v>0.0</v>
       </c>
@@ -1223,7 +1233,7 @@
           <t>Requested repayment term (years)</t>
         </is>
       </c>
-      <c r="C16" s="60" t="str">
+      <c r="C16" s="61" t="str">
         <f>IF('Loan Schedule'!$C$4=0,"—",'Loan Schedule'!$C$6)</f>
         <v>—</v>
       </c>
@@ -1234,7 +1244,7 @@
           <t>Projected Year 1 revenue (excl. sales tax)</t>
         </is>
       </c>
-      <c r="C17" s="59">
+      <c r="C17" s="60">
         <f>Projections!$B$4</f>
         <v>0.0</v>
       </c>
@@ -1245,7 +1255,7 @@
           <t>Projected Year 1 EBITDA</t>
         </is>
       </c>
-      <c r="C18" s="59">
+      <c r="C18" s="60">
         <f>Projections!$B$11</f>
         <v>0.0</v>
       </c>
@@ -1256,7 +1266,7 @@
           <t>Estimated payback period</t>
         </is>
       </c>
-      <c r="C19" s="61" t="str">
+      <c r="C19" s="62" t="str">
         <f>Projections!$B$26</f>
         <v>—</v>
       </c>
@@ -1402,19 +1412,19 @@
           <t>Revenue (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B4" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="62" t="n">
+      <c r="B4" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1424,19 +1434,19 @@
           <t>Food cost</t>
         </is>
       </c>
-      <c r="B5" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="62" t="n">
+      <c r="B5" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1446,19 +1456,19 @@
           <t>Beverage cost</t>
         </is>
       </c>
-      <c r="B6" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="62" t="n">
+      <c r="B6" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1468,19 +1478,19 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B7" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="62" t="n">
+      <c r="B7" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1490,19 +1500,19 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B8" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="62" t="n">
+      <c r="B8" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1512,19 +1522,19 @@
           <t>Other operating expenses</t>
         </is>
       </c>
-      <c r="B9" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="62" t="n">
+      <c r="B9" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1534,23 +1544,23 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B10" s="63">
+      <c r="B10" s="64">
         <f>SUM(B5:B9)</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="63">
+      <c r="C10" s="64">
         <f>SUM(C5:C9)</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="63">
+      <c r="D10" s="64">
         <f>SUM(D5:D9)</f>
         <v>0.0</v>
       </c>
-      <c r="E10" s="63">
+      <c r="E10" s="64">
         <f>SUM(E5:E9)</f>
         <v>0.0</v>
       </c>
-      <c r="F10" s="63">
+      <c r="F10" s="64">
         <f>SUM(F5:F9)</f>
         <v>0.0</v>
       </c>
@@ -1561,23 +1571,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B11" s="63">
+      <c r="B11" s="64">
         <f>B4-B10</f>
         <v>0.0</v>
       </c>
-      <c r="C11" s="63">
+      <c r="C11" s="64">
         <f>C4-C10</f>
         <v>0.0</v>
       </c>
-      <c r="D11" s="63">
+      <c r="D11" s="64">
         <f>D4-D10</f>
         <v>0.0</v>
       </c>
-      <c r="E11" s="63">
+      <c r="E11" s="64">
         <f>E4-E10</f>
         <v>0.0</v>
       </c>
-      <c r="F11" s="63">
+      <c r="F11" s="64">
         <f>F4-F10</f>
         <v>0.0</v>
       </c>
@@ -1588,19 +1598,19 @@
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="B12" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="62" t="n">
+      <c r="B12" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="63" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="29" t="inlineStr">
@@ -1615,23 +1625,23 @@
           <t>Interest on debt</t>
         </is>
       </c>
-      <c r="B13" s="63">
+      <c r="B13" s="64">
         <f>'Loan Schedule'!$D$12</f>
         <v>0.0</v>
       </c>
-      <c r="C13" s="63">
+      <c r="C13" s="64">
         <f>'Loan Schedule'!$D$13</f>
         <v>0.0</v>
       </c>
-      <c r="D13" s="63">
+      <c r="D13" s="64">
         <f>'Loan Schedule'!$D$14</f>
         <v>0.0</v>
       </c>
-      <c r="E13" s="63">
+      <c r="E13" s="64">
         <f>'Loan Schedule'!$D$15</f>
         <v>0.0</v>
       </c>
-      <c r="F13" s="63">
+      <c r="F13" s="64">
         <f>'Loan Schedule'!$D$16</f>
         <v>0.0</v>
       </c>
@@ -1642,23 +1652,23 @@
           <t>EBT (Earnings Before Tax)</t>
         </is>
       </c>
-      <c r="B14" s="63">
+      <c r="B14" s="64">
         <f>B11-B12-B13</f>
         <v>0.0</v>
       </c>
-      <c r="C14" s="63">
+      <c r="C14" s="64">
         <f>C11-C12-C13</f>
         <v>0.0</v>
       </c>
-      <c r="D14" s="63">
+      <c r="D14" s="64">
         <f>D11-D12-D13</f>
         <v>0.0</v>
       </c>
-      <c r="E14" s="63">
+      <c r="E14" s="64">
         <f>E11-E12-E13</f>
         <v>0.0</v>
       </c>
-      <c r="F14" s="63">
+      <c r="F14" s="64">
         <f>F11-F12-F13</f>
         <v>0.0</v>
       </c>
@@ -1669,23 +1679,23 @@
           <t>Income tax</t>
         </is>
       </c>
-      <c r="B15" s="63">
+      <c r="B15" s="64">
         <f>IF(B14&gt;0,B14*$C$29,0)</f>
         <v>0.0</v>
       </c>
-      <c r="C15" s="63">
+      <c r="C15" s="64">
         <f>IF(C14&gt;0,C14*$C$29,0)</f>
         <v>0.0</v>
       </c>
-      <c r="D15" s="63">
+      <c r="D15" s="64">
         <f>IF(D14&gt;0,D14*$C$29,0)</f>
         <v>0.0</v>
       </c>
-      <c r="E15" s="63">
+      <c r="E15" s="64">
         <f>IF(E14&gt;0,E14*$C$29,0)</f>
         <v>0.0</v>
       </c>
-      <c r="F15" s="63">
+      <c r="F15" s="64">
         <f>IF(F14&gt;0,F14*$C$29,0)</f>
         <v>0.0</v>
       </c>
@@ -1696,23 +1706,23 @@
           <t>NET INCOME</t>
         </is>
       </c>
-      <c r="B16" s="63">
+      <c r="B16" s="64">
         <f>B14-B15</f>
         <v>0.0</v>
       </c>
-      <c r="C16" s="63">
+      <c r="C16" s="64">
         <f>C14-C15</f>
         <v>0.0</v>
       </c>
-      <c r="D16" s="63">
+      <c r="D16" s="64">
         <f>D14-D15</f>
         <v>0.0</v>
       </c>
-      <c r="E16" s="63">
+      <c r="E16" s="64">
         <f>E14-E15</f>
         <v>0.0</v>
       </c>
-      <c r="F16" s="63">
+      <c r="F16" s="64">
         <f>F14-F15</f>
         <v>0.0</v>
       </c>
@@ -1723,23 +1733,23 @@
           <t>Project free cash flow (no debt)</t>
         </is>
       </c>
-      <c r="B17" s="63">
+      <c r="B17" s="64">
         <f>B11-MAX(0,(B11-B12)*$C$29)</f>
         <v>0.0</v>
       </c>
-      <c r="C17" s="63">
+      <c r="C17" s="64">
         <f>C11-MAX(0,(C11-C12)*$C$29)</f>
         <v>0.0</v>
       </c>
-      <c r="D17" s="63">
+      <c r="D17" s="64">
         <f>D11-MAX(0,(D11-D12)*$C$29)</f>
         <v>0.0</v>
       </c>
-      <c r="E17" s="63">
+      <c r="E17" s="64">
         <f>E11-MAX(0,(E11-E12)*$C$29)</f>
         <v>0.0</v>
       </c>
-      <c r="F17" s="63">
+      <c r="F17" s="64">
         <f>F11-MAX(0,(F11-F12)*$C$29)</f>
         <v>0.0</v>
       </c>
@@ -1755,23 +1765,23 @@
           <t>OPERATING CASH FLOW</t>
         </is>
       </c>
-      <c r="B18" s="63">
+      <c r="B18" s="64">
         <f>B16+B12</f>
         <v>0.0</v>
       </c>
-      <c r="C18" s="63">
+      <c r="C18" s="64">
         <f>C16+C12</f>
         <v>0.0</v>
       </c>
-      <c r="D18" s="63">
+      <c r="D18" s="64">
         <f>D16+D12</f>
         <v>0.0</v>
       </c>
-      <c r="E18" s="63">
+      <c r="E18" s="64">
         <f>E16+E12</f>
         <v>0.0</v>
       </c>
-      <c r="F18" s="63">
+      <c r="F18" s="64">
         <f>F16+F12</f>
         <v>0.0</v>
       </c>
@@ -1831,27 +1841,27 @@
           <t>Project cash flow</t>
         </is>
       </c>
-      <c r="B22" s="64">
+      <c r="B22" s="65">
         <f>-'Executive Summary'!$C$13</f>
         <v>0.0</v>
       </c>
-      <c r="C22" s="65">
+      <c r="C22" s="66">
         <f>B17</f>
         <v>0.0</v>
       </c>
-      <c r="D22" s="65">
+      <c r="D22" s="66">
         <f>C17</f>
         <v>0.0</v>
       </c>
-      <c r="E22" s="65">
+      <c r="E22" s="66">
         <f>D17</f>
         <v>0.0</v>
       </c>
-      <c r="F22" s="65">
+      <c r="F22" s="66">
         <f>E17</f>
         <v>0.0</v>
       </c>
-      <c r="G22" s="65">
+      <c r="G22" s="66">
         <f>F17</f>
         <v>0.0</v>
       </c>
@@ -1862,27 +1872,27 @@
           <t>Cumulative cash flow</t>
         </is>
       </c>
-      <c r="B23" s="63">
+      <c r="B23" s="64">
         <f>B22</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="65">
+      <c r="C23" s="66">
         <f>$B23+C22</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="65">
+      <c r="D23" s="66">
         <f>$C23+D22</f>
         <v>0.0</v>
       </c>
-      <c r="E23" s="65">
+      <c r="E23" s="66">
         <f>$D23+E22</f>
         <v>0.0</v>
       </c>
-      <c r="F23" s="65">
+      <c r="F23" s="66">
         <f>$E23+F22</f>
         <v>0.0</v>
       </c>
-      <c r="G23" s="65">
+      <c r="G23" s="66">
         <f>$F23+G22</f>
         <v>0.0</v>
       </c>
@@ -1904,7 +1914,7 @@
           <t>Project NPV</t>
         </is>
       </c>
-      <c r="B25" s="66">
+      <c r="B25" s="67">
         <f>IFERROR(NPV($C$27,$C$22:$G$22)+$B$22,"—")</f>
         <v>0.0</v>
       </c>
@@ -1915,7 +1925,7 @@
           <t>Project payback period (years)</t>
         </is>
       </c>
-      <c r="B26" s="67" t="str">
+      <c r="B26" s="68" t="str">
         <f>IFERROR(IF($G$23&lt;0,"Not paid back within 5 years",COUNTIF($B$23:$G$23,"&lt;0")-1+(-INDEX($B$23:$G$23,COUNTIF($B$23:$G$23,"&lt;0")))/INDEX($B$22:$G$22,COUNTIF($B$23:$G$23,"&lt;0")+1)),"—")</f>
         <v>—</v>
       </c>
@@ -2047,10 +2057,10 @@
           <t>Amount requested</t>
         </is>
       </c>
-      <c r="C4" s="68" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="69" t="inlineStr">
+      <c r="C4" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="70" t="inlineStr">
         <is>
           <t>The amount you ask the lender for.</t>
         </is>
@@ -2065,7 +2075,7 @@
       <c r="C5" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="D5" s="69" t="inlineStr">
+      <c r="D5" s="70" t="inlineStr">
         <is>
           <t>Nominal rate, not APR. (example: change it)</t>
         </is>
@@ -2080,7 +2090,7 @@
       <c r="C6" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="69" t="inlineStr">
+      <c r="D6" s="70" t="inlineStr">
         <is>
           <t>TOTAL term, interest-only period included. SBA 7(a): up to 10 years for equipment and working capital. (example: change it)</t>
         </is>
@@ -2095,7 +2105,7 @@
       <c r="C7" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="69" t="inlineStr">
+      <c r="D7" s="70" t="inlineStr">
         <is>
           <t>Initial years in which you pay interest only; afterwards the payment is calculated over the remaining term.</t>
         </is>
@@ -2107,11 +2117,11 @@
           <t>ANNUAL PAYMENT</t>
         </is>
       </c>
-      <c r="C8" s="66">
-        <f>IF(($C$6-$C$7)&lt;=0,"The interest-only period must be shorter than the term",IFERROR($C$4*$C$5/(1-(1+$C$5)^(-($C$6-$C$7))),0))</f>
-        <v>0.0</v>
-      </c>
-      <c r="D8" s="69" t="inlineStr">
+      <c r="C8" s="67">
+        <f>IF(($C$6-$C$7)&lt;=0,"The interest-only period must be shorter than the term",IF($C$5=0,$C$4/($C$6-$C$7),IFERROR($C$4*$C$5/(1-(1+$C$5)^(-($C$6-$C$7))),0)))</f>
+        <v>0.0</v>
+      </c>
+      <c r="D8" s="70" t="inlineStr">
         <is>
           <t>Level annual payment (standard amortization) over the term left after the interest-only period, which must be SHORTER than the term: otherwise no year is left to repay the principal and you get a warning here instead.</t>
         </is>
@@ -2160,23 +2170,23 @@
       <c r="A12" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="65">
+      <c r="B12" s="66">
         <f>$C$4</f>
         <v>0.0</v>
       </c>
-      <c r="C12" s="65">
+      <c r="C12" s="66">
         <f>IF($C$6&lt;=$C$7,"—",IF($A12&gt;$C$6,0,IF($A12&lt;=$C$7,$B12*$C$5,$C$8)))</f>
         <v>0.0</v>
       </c>
-      <c r="D12" s="65">
+      <c r="D12" s="66">
         <f>IF($A12&gt;$C$6,0,$B12*$C$5)</f>
         <v>0.0</v>
       </c>
-      <c r="E12" s="65">
+      <c r="E12" s="66">
         <f>IF($C$6&lt;=$C$7,0,IF($A12&gt;$C$6,0,$C12-$D12))</f>
         <v>0.0</v>
       </c>
-      <c r="F12" s="65">
+      <c r="F12" s="66">
         <f>$B12-$E12</f>
         <v>0.0</v>
       </c>
@@ -2185,23 +2195,23 @@
       <c r="A13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="65">
+      <c r="B13" s="66">
         <f>$F$12</f>
         <v>0.0</v>
       </c>
-      <c r="C13" s="65">
+      <c r="C13" s="66">
         <f>IF($C$6&lt;=$C$7,"—",IF($A13&gt;$C$6,0,IF($A13&lt;=$C$7,$B13*$C$5,$C$8)))</f>
         <v>0.0</v>
       </c>
-      <c r="D13" s="65">
+      <c r="D13" s="66">
         <f>IF($A13&gt;$C$6,0,$B13*$C$5)</f>
         <v>0.0</v>
       </c>
-      <c r="E13" s="65">
+      <c r="E13" s="66">
         <f>IF($C$6&lt;=$C$7,0,IF($A13&gt;$C$6,0,$C13-$D13))</f>
         <v>0.0</v>
       </c>
-      <c r="F13" s="65">
+      <c r="F13" s="66">
         <f>$B13-$E13</f>
         <v>0.0</v>
       </c>
@@ -2210,23 +2220,23 @@
       <c r="A14" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="65">
+      <c r="B14" s="66">
         <f>$F$13</f>
         <v>0.0</v>
       </c>
-      <c r="C14" s="65">
+      <c r="C14" s="66">
         <f>IF($C$6&lt;=$C$7,"—",IF($A14&gt;$C$6,0,IF($A14&lt;=$C$7,$B14*$C$5,$C$8)))</f>
         <v>0.0</v>
       </c>
-      <c r="D14" s="65">
+      <c r="D14" s="66">
         <f>IF($A14&gt;$C$6,0,$B14*$C$5)</f>
         <v>0.0</v>
       </c>
-      <c r="E14" s="65">
+      <c r="E14" s="66">
         <f>IF($C$6&lt;=$C$7,0,IF($A14&gt;$C$6,0,$C14-$D14))</f>
         <v>0.0</v>
       </c>
-      <c r="F14" s="65">
+      <c r="F14" s="66">
         <f>$B14-$E14</f>
         <v>0.0</v>
       </c>
@@ -2235,23 +2245,23 @@
       <c r="A15" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="65">
+      <c r="B15" s="66">
         <f>$F$14</f>
         <v>0.0</v>
       </c>
-      <c r="C15" s="65">
+      <c r="C15" s="66">
         <f>IF($C$6&lt;=$C$7,"—",IF($A15&gt;$C$6,0,IF($A15&lt;=$C$7,$B15*$C$5,$C$8)))</f>
         <v>0.0</v>
       </c>
-      <c r="D15" s="65">
+      <c r="D15" s="66">
         <f>IF($A15&gt;$C$6,0,$B15*$C$5)</f>
         <v>0.0</v>
       </c>
-      <c r="E15" s="65">
+      <c r="E15" s="66">
         <f>IF($C$6&lt;=$C$7,0,IF($A15&gt;$C$6,0,$C15-$D15))</f>
         <v>0.0</v>
       </c>
-      <c r="F15" s="65">
+      <c r="F15" s="66">
         <f>$B15-$E15</f>
         <v>0.0</v>
       </c>
@@ -2260,23 +2270,23 @@
       <c r="A16" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="65">
+      <c r="B16" s="66">
         <f>$F$15</f>
         <v>0.0</v>
       </c>
-      <c r="C16" s="65">
+      <c r="C16" s="66">
         <f>IF($C$6&lt;=$C$7,"—",IF($A16&gt;$C$6,0,IF($A16&lt;=$C$7,$B16*$C$5,$C$8)))</f>
         <v>0.0</v>
       </c>
-      <c r="D16" s="65">
+      <c r="D16" s="66">
         <f>IF($A16&gt;$C$6,0,$B16*$C$5)</f>
         <v>0.0</v>
       </c>
-      <c r="E16" s="65">
+      <c r="E16" s="66">
         <f>IF($C$6&lt;=$C$7,0,IF($A16&gt;$C$6,0,$C16-$D16))</f>
         <v>0.0</v>
       </c>
-      <c r="F16" s="65">
+      <c r="F16" s="66">
         <f>$B16-$E16</f>
         <v>0.0</v>
       </c>
@@ -2284,7 +2294,7 @@
     <row r="18">
       <c r="B18" s="29" t="inlineStr">
         <is>
-          <t>The payment in column C is the one copied to file 03 "Cash Flow Forecast", "Monthly Cash Flow" tab, row 23 (divided by 12), and the one that divides the DSCR in the "Ratios" tab.</t>
+          <t>Copy the payment in column C into file 03 "Cash Flow Forecast", "Monthly Cash Flow" tab, row 23 (divided by 12). The DSCR in the "Ratios" tab divides by the full ANNUAL PAYMENT in cell C8, not by an interest-only year.</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2370,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="27.25" customHeight="1">
       <c r="A3" s="47" t="n"/>
       <c r="B3" s="48" t="inlineStr">
         <is>
@@ -2374,7 +2384,7 @@
       </c>
       <c r="D3" s="48" t="inlineStr">
         <is>
-          <t>Lender benchmark</t>
+          <t>Typical lender guideline (indicative)</t>
         </is>
       </c>
       <c r="E3" s="46" t="inlineStr">
@@ -2432,11 +2442,11 @@
     <row r="5">
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Debt service coverage (DSCR)</t>
+          <t>DSCR at full payment</t>
         </is>
       </c>
       <c r="C5" s="52" t="str">
-        <f>IFERROR(Projections!$B$17/'Loan Schedule'!$C$12,"Enter the loan")</f>
+        <f>IFERROR(Projections!$B$17/'Loan Schedule'!$C$8,"Enter the loan")</f>
         <v>Enter the loan</v>
       </c>
       <c r="D5" s="50" t="inlineStr">
@@ -2629,7 +2639,7 @@
           <t>Current assets</t>
         </is>
       </c>
-      <c r="C13" s="68" t="n">
+      <c r="C13" s="69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2639,7 +2649,7 @@
           <t>Current liabilities</t>
         </is>
       </c>
-      <c r="C14" s="68" t="n">
+      <c r="C14" s="69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2649,8 +2659,9 @@
           <t>Owner's equity</t>
         </is>
       </c>
-      <c r="C15" s="68" t="n">
-        <v>0</v>
+      <c r="C15" s="66">
+        <f>'Executive Summary'!$C$14</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -2659,8 +2670,9 @@
           <t>Outstanding debt</t>
         </is>
       </c>
-      <c r="C16" s="68" t="n">
-        <v>0</v>
+      <c r="C16" s="66">
+        <f>'Loan Schedule'!$C$4</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -2669,7 +2681,7 @@
           <t>Total project investment</t>
         </is>
       </c>
-      <c r="C17" s="65">
+      <c r="C17" s="66">
         <f>'Executive Summary'!$C$13</f>
         <v>0.0</v>
       </c>
@@ -2684,7 +2696,7 @@
     <row r="21">
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>DSCR divides the project's year 1 FREE CASH FLOW ("Projections", row 17: EBITDA minus income tax, computed before interest) by that same year's debt service ("Loan Schedule", column "Annual payment", year 1). The numerator is taken BEFORE debt on purpose: if you subtracted interest from it, you would be counting it twice.</t>
+          <t>DSCR divides the project's year 1 FREE CASH FLOW ("Projections", row 17: EBITDA minus income tax, computed before interest) by the FULL annual loan payment ("Loan Schedule", "ANNUAL PAYMENT"), even if year 1 is interest-only: lenders look at the full payment. The numerator is taken BEFORE debt on purpose: if you subtracted interest from it, you would be counting it twice.</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2793,7 @@
           <t>Personal guarantee (SBA: owners of 20%+)</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n">
+      <c r="C4" s="71" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="56" t="n"/>
@@ -2792,7 +2804,7 @@
           <t>Mortgage on the premises (if owned)</t>
         </is>
       </c>
-      <c r="C5" s="70" t="n">
+      <c r="C5" s="71" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="56" t="n"/>
@@ -2803,7 +2815,7 @@
           <t>Pledged deposits / cash collateral</t>
         </is>
       </c>
-      <c r="C6" s="70" t="n">
+      <c r="C6" s="71" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="56" t="n"/>
@@ -2814,7 +2826,7 @@
           <t>Blanket lien on business assets (UCC-1)</t>
         </is>
       </c>
-      <c r="C7" s="70" t="n">
+      <c r="C7" s="71" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="56" t="n"/>
@@ -2825,7 +2837,7 @@
           <t>Assignment of life insurance (SBA lenders)</t>
         </is>
       </c>
-      <c r="C8" s="70" t="n">
+      <c r="C8" s="71" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="56" t="n"/>
@@ -2836,7 +2848,7 @@
           <t>Additional deposit</t>
         </is>
       </c>
-      <c r="C9" s="70" t="n">
+      <c r="C9" s="71" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="56" t="n"/>
@@ -2847,7 +2859,7 @@
           <t>TOTAL COLLATERAL</t>
         </is>
       </c>
-      <c r="C10" s="71">
+      <c r="C10" s="72">
         <f>SUM(C4:C9)</f>
         <v>0.0</v>
       </c>
